--- a/disc_experiments_metrics.xlsx
+++ b/disc_experiments_metrics.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="64">
   <si>
     <t>AGE BINS DATASET / EXPERIMENTS ON NUMERIC DESCRETIZATION EFFECT</t>
   </si>
@@ -189,6 +189,36 @@
   </si>
   <si>
     <t>Quant100 sum</t>
+  </si>
+  <si>
+    <t>GLOVE EMBEDDING</t>
+  </si>
+  <si>
+    <t>DISC</t>
+  </si>
+  <si>
+    <t>AGG TYPE</t>
+  </si>
+  <si>
+    <t>NOISY EMBEDDING</t>
+  </si>
+  <si>
+    <t>TRAN EMBEDDING</t>
+  </si>
+  <si>
+    <t>NOISY EMBEDDING + PLE</t>
+  </si>
+  <si>
+    <t>DISC/AGG</t>
+  </si>
+  <si>
+    <t>Quant/CAT</t>
+  </si>
+  <si>
+    <t>SingleTree/SUM</t>
+  </si>
+  <si>
+    <t>SingleTree/MEAN</t>
   </si>
 </sst>
 </file>
@@ -202,14 +232,7 @@
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,7 +603,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -649,6 +672,185 @@
       </left>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -770,137 +972,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -942,12 +1144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -964,6 +1161,166 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1503,20 +1860,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U112"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85714285714286" customWidth="1"/>
     <col min="2" max="2" width="27.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="9.28571428571429" customWidth="1"/>
     <col min="4" max="4" width="9.85714285714286" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="5" max="5" width="27.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="11.1428571428571" customWidth="1"/>
     <col min="7" max="7" width="12.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12.4285714285714" customWidth="1"/>
     <col min="10" max="10" width="13.1428571428571" customWidth="1"/>
-    <col min="12" max="12" width="9.28571428571429" customWidth="1"/>
+    <col min="11" max="11" width="10.8571428571429" customWidth="1"/>
+    <col min="12" max="12" width="11.7142857142857" customWidth="1"/>
+    <col min="13" max="13" width="12.2857142857143" customWidth="1"/>
+    <col min="14" max="14" width="10.1428571428571" customWidth="1"/>
     <col min="16" max="16" width="10.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2022,7 +2382,7 @@
       <c r="O11" s="4">
         <v>0.606333333333333</v>
       </c>
-      <c r="P11" s="25">
+      <c r="P11" s="22">
         <v>0.6075</v>
       </c>
       <c r="Q11" s="4">
@@ -2365,7 +2725,7 @@
       <c r="I19" s="11">
         <v>0.592681586742401</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="23">
         <v>0.637353539466858</v>
       </c>
       <c r="K19" s="4">
@@ -2424,7 +2784,7 @@
       <c r="I20" s="4">
         <v>0.561766666666667</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="24">
         <v>0.584333333333333</v>
       </c>
       <c r="K20" s="4">
@@ -2483,7 +2843,7 @@
       <c r="I21" s="4">
         <v>0.581166666666667</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="24">
         <v>0.604166666666667</v>
       </c>
       <c r="K21" s="4">
@@ -2501,7 +2861,7 @@
       <c r="O21" s="4">
         <v>0.591</v>
       </c>
-      <c r="P21" s="25">
+      <c r="P21" s="22">
         <v>0.593909483839828</v>
       </c>
       <c r="Q21" s="4">
@@ -2519,7 +2879,7 @@
     </row>
     <row r="22" spans="5:20">
       <c r="E22" s="16"/>
-      <c r="I22" s="28"/>
+      <c r="I22" s="25"/>
       <c r="J22" s="18"/>
       <c r="M22" s="16"/>
       <c r="P22" s="16"/>
@@ -2549,7 +2909,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="31"/>
+      <c r="T23" s="28"/>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="1"/>
@@ -3069,9 +3429,9 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="32"/>
-      <c r="T35" s="32"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" s="1" t="s">
@@ -3123,11 +3483,11 @@
       <c r="Q36" t="s">
         <v>26</v>
       </c>
-      <c r="S36" s="33" t="s">
+      <c r="S36" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" t="s">
@@ -3181,11 +3541,11 @@
       <c r="Q37" s="4">
         <v>0.579507622718811</v>
       </c>
-      <c r="S37" s="33" t="s">
+      <c r="S37" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="T37" s="33"/>
-      <c r="U37" s="33"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
     </row>
     <row r="38" spans="2:21">
       <c r="B38" t="s">
@@ -3236,11 +3596,11 @@
       <c r="Q38" s="4">
         <v>0.986787217886745</v>
       </c>
-      <c r="S38" s="33" t="s">
+      <c r="S38" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="T38" s="33"/>
-      <c r="U38" s="33"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
     </row>
     <row r="39" spans="2:17">
       <c r="B39" t="s">
@@ -3329,7 +3689,7 @@
       <c r="L40" s="17">
         <v>0.740744769573212</v>
       </c>
-      <c r="M40" s="29">
+      <c r="M40" s="26">
         <v>0.497865063548088</v>
       </c>
       <c r="N40" s="11">
@@ -3385,13 +3745,13 @@
       <c r="N41" s="11">
         <v>0.537966666666667</v>
       </c>
-      <c r="O41" s="30">
+      <c r="O41" s="27">
         <v>0.5795</v>
       </c>
-      <c r="P41" s="30">
+      <c r="P41" s="27">
         <v>0.532933333333333</v>
       </c>
-      <c r="Q41" s="30">
+      <c r="Q41" s="27">
         <v>0.5619</v>
       </c>
     </row>
@@ -3435,13 +3795,13 @@
       <c r="N42" s="11">
         <v>0.535833333333333</v>
       </c>
-      <c r="O42" s="30">
+      <c r="O42" s="27">
         <v>0.58</v>
       </c>
-      <c r="P42" s="30">
+      <c r="P42" s="27">
         <v>0.521333333333333</v>
       </c>
-      <c r="Q42" s="30">
+      <c r="Q42" s="27">
         <v>0.541666666666667</v>
       </c>
     </row>
@@ -3479,7 +3839,7 @@
       <c r="B47" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="21">
         <v>0.576366666666667</v>
       </c>
     </row>
@@ -3488,7 +3848,7 @@
       <c r="B48" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="21">
         <v>0.597833333333333</v>
       </c>
     </row>
@@ -3522,18 +3882,18 @@
       <c r="B52" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23" t="s">
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
     </row>
     <row r="53" spans="2:10">
       <c r="B53" t="s">
@@ -3571,28 +3931,28 @@
       <c r="B54" t="s">
         <v>22</v>
       </c>
-      <c r="C54" s="24">
+      <c r="C54" s="4">
         <v>0.25943660736084</v>
       </c>
-      <c r="D54" s="24">
+      <c r="D54" s="4">
         <v>0.250308126211166</v>
       </c>
-      <c r="E54" s="24">
+      <c r="E54" s="4">
         <v>0.141106307506561</v>
       </c>
-      <c r="F54" s="24">
+      <c r="F54" s="4">
         <v>0.240581974387169</v>
       </c>
-      <c r="G54" s="24">
+      <c r="G54" s="4">
         <v>0.305890798568726</v>
       </c>
-      <c r="H54" s="24">
+      <c r="H54" s="4">
         <v>0.128335431218147</v>
       </c>
-      <c r="I54" s="24">
+      <c r="I54" s="4">
         <v>0.323220103979111</v>
       </c>
-      <c r="J54" s="24">
+      <c r="J54" s="4">
         <v>0.134350582957268</v>
       </c>
     </row>
@@ -3600,28 +3960,28 @@
       <c r="B55" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C55" s="4">
         <v>0.496766666666667</v>
       </c>
-      <c r="D55" s="24">
+      <c r="D55" s="4">
         <v>0.516466666666667</v>
       </c>
-      <c r="E55" s="24">
+      <c r="E55" s="4">
         <v>0.4787</v>
       </c>
-      <c r="F55" s="24">
+      <c r="F55" s="4">
         <v>0.510533333333333</v>
       </c>
-      <c r="G55" s="24">
+      <c r="G55" s="4">
         <v>0.519966666666667</v>
       </c>
-      <c r="H55" s="24">
+      <c r="H55" s="4">
         <v>0.4774</v>
       </c>
-      <c r="I55" s="24">
+      <c r="I55" s="4">
         <v>0.532566666666667</v>
       </c>
-      <c r="J55" s="24">
+      <c r="J55" s="4">
         <v>0.481066666666667</v>
       </c>
     </row>
@@ -3629,33 +3989,889 @@
       <c r="B56" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="24">
+      <c r="C56" s="4">
         <v>0.505166666666667</v>
       </c>
-      <c r="D56" s="24">
+      <c r="D56" s="4">
         <v>0.539</v>
       </c>
-      <c r="E56" s="24">
+      <c r="E56" s="4">
         <v>0.4895</v>
       </c>
-      <c r="F56" s="24">
+      <c r="F56" s="4">
         <v>0.519333333333333</v>
       </c>
-      <c r="G56" s="24">
+      <c r="G56" s="4">
         <v>0.548666666666667</v>
       </c>
-      <c r="H56" s="24">
+      <c r="H56" s="4">
         <v>0.486833333333333</v>
       </c>
-      <c r="I56" s="24">
+      <c r="I56" s="4">
         <v>0.544333333333333</v>
       </c>
-      <c r="J56" s="24">
+      <c r="J56" s="4">
         <v>0.492833333333333</v>
       </c>
     </row>
+    <row r="63" spans="8:10">
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="65" spans="5:7">
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="5:7">
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" spans="5:7">
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="69" spans="4:12">
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+    </row>
+    <row r="70" spans="4:12">
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+    </row>
+    <row r="71" spans="10:12">
+      <c r="J71" s="20"/>
+      <c r="K71" s="20"/>
+      <c r="L71" s="20"/>
+    </row>
+    <row r="72" spans="6:12">
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="20"/>
+      <c r="L72" s="21"/>
+    </row>
+    <row r="73" spans="6:12">
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="20"/>
+      <c r="L73" s="21"/>
+    </row>
+    <row r="74" ht="15.75" spans="6:12">
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="20"/>
+      <c r="L74" s="21"/>
+    </row>
+    <row r="75" spans="4:15">
+      <c r="D75" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E75" s="33"/>
+      <c r="F75" s="33"/>
+      <c r="G75" s="33"/>
+      <c r="H75" s="33"/>
+      <c r="I75" s="33"/>
+      <c r="J75" s="33"/>
+      <c r="K75" s="33"/>
+      <c r="L75" s="33"/>
+      <c r="M75" s="33"/>
+      <c r="N75" s="33"/>
+      <c r="O75" s="74"/>
+    </row>
+    <row r="76" spans="4:15">
+      <c r="D76" s="34"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="19"/>
+      <c r="M76" s="19"/>
+      <c r="N76" s="19"/>
+      <c r="O76" s="75"/>
+    </row>
+    <row r="77" spans="4:15">
+      <c r="D77" s="35"/>
+      <c r="E77" t="s">
+        <v>55</v>
+      </c>
+      <c r="F77" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H77" s="19"/>
+      <c r="I77" s="76"/>
+      <c r="J77" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77" s="19"/>
+      <c r="L77" s="76"/>
+      <c r="M77" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="N77" s="19"/>
+      <c r="O77" s="75"/>
+    </row>
+    <row r="78" spans="4:15">
+      <c r="D78" s="35"/>
+      <c r="E78" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F78" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H78" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="K78" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="L78" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="M78" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="N78" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="O78" s="77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="4:15">
+      <c r="D79" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="37">
+        <v>0.644263923168182</v>
+      </c>
+      <c r="G79" s="38">
+        <v>0.743707120418549</v>
+      </c>
+      <c r="H79" s="4">
+        <v>0.420129584646225</v>
+      </c>
+      <c r="I79" s="11">
+        <v>0.497344888448715</v>
+      </c>
+      <c r="J79" s="4">
+        <v>0.740207120418549</v>
+      </c>
+      <c r="K79" s="4">
+        <v>0.519529584646225</v>
+      </c>
+      <c r="L79" s="60">
+        <v>0.505784994363785</v>
+      </c>
+      <c r="M79" s="50">
+        <v>0.752542555332184</v>
+      </c>
+      <c r="N79" s="78">
+        <v>0.393069902062416</v>
+      </c>
+      <c r="O79" s="79">
+        <v>0.579294029474258</v>
+      </c>
+    </row>
+    <row r="80" spans="4:15">
+      <c r="D80" s="35"/>
+      <c r="E80" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="37">
+        <v>0.541833333333333</v>
+      </c>
+      <c r="G80" s="38">
+        <v>0.582033333333333</v>
+      </c>
+      <c r="H80" s="4">
+        <v>0.5524</v>
+      </c>
+      <c r="I80" s="11">
+        <v>0.535466666666667</v>
+      </c>
+      <c r="J80" s="4">
+        <v>0.581033333333333</v>
+      </c>
+      <c r="K80" s="4">
+        <v>0.5324</v>
+      </c>
+      <c r="L80" s="60">
+        <v>0.534366666666667</v>
+      </c>
+      <c r="M80" s="50">
+        <v>0.5795</v>
+      </c>
+      <c r="N80" s="50">
+        <v>0.532933333333333</v>
+      </c>
+      <c r="O80" s="80">
+        <v>0.5619</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" spans="4:15">
+      <c r="D81" s="39"/>
+      <c r="E81" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="41">
+        <v>0.554666666666667</v>
+      </c>
+      <c r="G81" s="42">
+        <v>0.594833333333333</v>
+      </c>
+      <c r="H81" s="43">
+        <v>0.5601</v>
+      </c>
+      <c r="I81" s="81">
+        <v>0.544666666666667</v>
+      </c>
+      <c r="J81" s="43">
+        <v>0.591833333333333</v>
+      </c>
+      <c r="K81" s="43">
+        <v>0.54</v>
+      </c>
+      <c r="L81" s="61">
+        <v>0.54</v>
+      </c>
+      <c r="M81" s="82">
+        <v>0.58</v>
+      </c>
+      <c r="N81" s="82">
+        <v>0.521333333333333</v>
+      </c>
+      <c r="O81" s="83">
+        <v>0.541666666666667</v>
+      </c>
+    </row>
+    <row r="82" spans="4:15">
+      <c r="D82" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="45"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="45"/>
+      <c r="L82" s="45"/>
+      <c r="M82" s="45"/>
+      <c r="N82" s="45"/>
+      <c r="O82" s="62"/>
+    </row>
+    <row r="83" spans="4:15">
+      <c r="D83" s="46"/>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31"/>
+      <c r="H83" s="31"/>
+      <c r="I83" s="31"/>
+      <c r="J83" s="31"/>
+      <c r="K83" s="31"/>
+      <c r="L83" s="31"/>
+      <c r="M83" s="31"/>
+      <c r="N83" s="31"/>
+      <c r="O83" s="63"/>
+    </row>
+    <row r="84" spans="4:21">
+      <c r="D84" s="47"/>
+      <c r="E84" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="G84" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="19"/>
+      <c r="I84" s="76"/>
+      <c r="J84" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="K84" s="19"/>
+      <c r="L84" s="76"/>
+      <c r="M84" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="N84" s="19"/>
+      <c r="O84" s="75"/>
+      <c r="P84" s="29"/>
+      <c r="Q84" s="29"/>
+      <c r="R84" s="29"/>
+      <c r="S84" s="29"/>
+      <c r="T84" s="29"/>
+      <c r="U84" s="29"/>
+    </row>
+    <row r="85" spans="4:21">
+      <c r="D85" s="47"/>
+      <c r="E85" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F85" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H85" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="J85" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="K85" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="L85" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="N85" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="O85" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="P85" s="29"/>
+      <c r="Q85" s="29"/>
+      <c r="R85" s="29"/>
+      <c r="S85" s="29"/>
+      <c r="T85" s="29"/>
+      <c r="U85" s="29"/>
+    </row>
+    <row r="86" spans="4:21">
+      <c r="D86" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F86" s="49">
+        <v>0.688462555408478</v>
+      </c>
+      <c r="G86" s="50">
+        <v>0.730457241535187</v>
+      </c>
+      <c r="H86" s="51">
+        <v>0.603714406490326</v>
+      </c>
+      <c r="I86" s="84">
+        <v>0.637353539466858</v>
+      </c>
+      <c r="J86" s="50">
+        <v>0.723375976085663</v>
+      </c>
+      <c r="K86" s="50">
+        <v>0.680322229862213</v>
+      </c>
+      <c r="L86" s="85">
+        <v>0.692839682102203</v>
+      </c>
+      <c r="M86" s="86">
+        <v>0.733893692493439</v>
+      </c>
+      <c r="N86" s="87">
+        <v>0.68617582321167</v>
+      </c>
+      <c r="O86" s="88">
+        <v>0.696798324584961</v>
+      </c>
+      <c r="P86" s="29"/>
+      <c r="Q86" s="29"/>
+      <c r="R86" s="29"/>
+      <c r="S86" s="29"/>
+      <c r="T86" s="29"/>
+      <c r="U86" s="29"/>
+    </row>
+    <row r="87" spans="4:15">
+      <c r="D87" s="35"/>
+      <c r="E87" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" s="49">
+        <v>0.576366666666667</v>
+      </c>
+      <c r="G87" s="50">
+        <v>0.5925</v>
+      </c>
+      <c r="H87" s="51">
+        <v>0.573833333333333</v>
+      </c>
+      <c r="I87" s="84">
+        <v>0.584333333333333</v>
+      </c>
+      <c r="J87" s="50">
+        <v>0.581366666666667</v>
+      </c>
+      <c r="K87" s="50">
+        <v>0.5877</v>
+      </c>
+      <c r="L87" s="85">
+        <v>0.587466666666667</v>
+      </c>
+      <c r="M87" s="86">
+        <v>0.593866666666667</v>
+      </c>
+      <c r="N87" s="89">
+        <v>0.581166666666667</v>
+      </c>
+      <c r="O87" s="90">
+        <v>0.5837</v>
+      </c>
+    </row>
+    <row r="88" spans="4:15">
+      <c r="D88" s="35"/>
+      <c r="E88" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="49">
+        <v>0.597833333333333</v>
+      </c>
+      <c r="G88" s="50">
+        <v>0.616333333333333</v>
+      </c>
+      <c r="H88" s="51">
+        <v>0.5835</v>
+      </c>
+      <c r="I88" s="84">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="J88" s="78">
+        <v>0.591166666666667</v>
+      </c>
+      <c r="K88" s="50">
+        <v>0.596833333333333</v>
+      </c>
+      <c r="L88" s="85">
+        <v>0.615333333333333</v>
+      </c>
+      <c r="M88" s="86">
+        <v>0.608333333333333</v>
+      </c>
+      <c r="N88" s="89">
+        <v>0.589666666666667</v>
+      </c>
+      <c r="O88" s="90">
+        <v>0.606</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" spans="4:15">
+      <c r="D89" s="52"/>
+      <c r="E89" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F89" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="55"/>
+      <c r="H89" s="56"/>
+      <c r="I89" s="91" t="s">
+        <v>12</v>
+      </c>
+      <c r="J89" s="91"/>
+      <c r="K89" s="92"/>
+      <c r="L89" s="93"/>
+      <c r="M89" s="93"/>
+      <c r="N89" s="93"/>
+      <c r="O89" s="94"/>
+    </row>
+    <row r="90" spans="4:15">
+      <c r="D90" s="57"/>
+      <c r="E90" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F90" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H90" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="I90" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="J90" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="K90" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="L90" s="31"/>
+      <c r="M90" s="31"/>
+      <c r="N90" s="31"/>
+      <c r="O90" s="63"/>
+    </row>
+    <row r="91" spans="4:15">
+      <c r="D91" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F91" s="37">
+        <v>0.605236232280731</v>
+      </c>
+      <c r="G91" s="4">
+        <v>0.56407755613327</v>
+      </c>
+      <c r="H91" s="60">
+        <v>0.579309642314911</v>
+      </c>
+      <c r="I91" s="26">
+        <v>0.613462686538696</v>
+      </c>
+      <c r="J91" s="26">
+        <v>0.549600064754486</v>
+      </c>
+      <c r="K91" s="11">
+        <v>0.592681586742401</v>
+      </c>
+      <c r="L91" s="31"/>
+      <c r="M91" s="31"/>
+      <c r="N91" s="31"/>
+      <c r="O91" s="63"/>
+    </row>
+    <row r="92" spans="4:15">
+      <c r="D92" s="35"/>
+      <c r="E92" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F92" s="37">
+        <v>0.5514</v>
+      </c>
+      <c r="G92" s="4">
+        <v>0.549266666666667</v>
+      </c>
+      <c r="H92" s="60">
+        <v>0.552033333333333</v>
+      </c>
+      <c r="I92" s="26">
+        <v>0.562033333333333</v>
+      </c>
+      <c r="J92" s="26">
+        <v>0.5411</v>
+      </c>
+      <c r="K92" s="96">
+        <v>0.561766666666667</v>
+      </c>
+      <c r="L92" s="31"/>
+      <c r="M92" s="31"/>
+      <c r="N92" s="31"/>
+      <c r="O92" s="63"/>
+    </row>
+    <row r="93" ht="15.75" spans="4:15">
+      <c r="D93" s="39"/>
+      <c r="E93" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="41">
+        <v>0.574666666666667</v>
+      </c>
+      <c r="G93" s="43">
+        <v>0.560166666666667</v>
+      </c>
+      <c r="H93" s="61">
+        <v>0.571333333333333</v>
+      </c>
+      <c r="I93" s="97">
+        <v>0.58</v>
+      </c>
+      <c r="J93" s="97">
+        <v>0.5495</v>
+      </c>
+      <c r="K93" s="98">
+        <v>0.581166666666667</v>
+      </c>
+      <c r="L93" s="99"/>
+      <c r="M93" s="99"/>
+      <c r="N93" s="99"/>
+      <c r="O93" s="100"/>
+    </row>
+    <row r="94" spans="4:15">
+      <c r="D94" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="E94" s="45"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="62"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
+      <c r="N94" s="45"/>
+      <c r="O94" s="62"/>
+    </row>
+    <row r="95" spans="4:15">
+      <c r="D95" s="46"/>
+      <c r="E95" s="31"/>
+      <c r="F95" s="31"/>
+      <c r="G95" s="31"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="31"/>
+      <c r="J95" s="46"/>
+      <c r="K95" s="31"/>
+      <c r="L95" s="31"/>
+      <c r="M95" s="31"/>
+      <c r="N95" s="31"/>
+      <c r="O95" s="63"/>
+    </row>
+    <row r="96" spans="4:15">
+      <c r="D96" s="64"/>
+      <c r="E96" t="s">
+        <v>55</v>
+      </c>
+      <c r="F96" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G96" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="I96" s="31"/>
+      <c r="J96" s="64"/>
+      <c r="K96" t="s">
+        <v>60</v>
+      </c>
+      <c r="L96" s="101" t="s">
+        <v>61</v>
+      </c>
+      <c r="M96" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N96" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="O96" s="63"/>
+    </row>
+    <row r="97" spans="4:15">
+      <c r="D97" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" s="67">
+        <v>0.25943660736084</v>
+      </c>
+      <c r="G97" s="4">
+        <v>0.250308126211166</v>
+      </c>
+      <c r="H97" s="68">
+        <v>0.141106307506561</v>
+      </c>
+      <c r="I97" s="31"/>
+      <c r="J97" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K97" t="s">
+        <v>22</v>
+      </c>
+      <c r="L97" s="102">
+        <v>0.706258058547974</v>
+      </c>
+      <c r="M97" s="50">
+        <v>0.676983416080475</v>
+      </c>
+      <c r="N97" s="78">
+        <v>0.631490647792816</v>
+      </c>
+      <c r="O97" s="63"/>
+    </row>
+    <row r="98" spans="4:15">
+      <c r="D98" s="64"/>
+      <c r="E98" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98" s="67">
+        <v>0.496766666666667</v>
+      </c>
+      <c r="G98" s="4">
+        <v>0.516466666666667</v>
+      </c>
+      <c r="H98" s="68">
+        <v>0.4787</v>
+      </c>
+      <c r="I98" s="31"/>
+      <c r="J98" s="64"/>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" s="103">
+        <v>0.590666666666667</v>
+      </c>
+      <c r="M98" s="50">
+        <v>0.5844</v>
+      </c>
+      <c r="N98" s="50">
+        <v>0.5885</v>
+      </c>
+      <c r="O98" s="63"/>
+    </row>
+    <row r="99" ht="15.75" spans="4:15">
+      <c r="D99" s="69"/>
+      <c r="E99" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="71">
+        <v>0.505166666666667</v>
+      </c>
+      <c r="G99" s="43">
+        <v>0.539</v>
+      </c>
+      <c r="H99" s="72">
+        <v>0.4895</v>
+      </c>
+      <c r="I99" s="99"/>
+      <c r="J99" s="69"/>
+      <c r="K99" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L99" s="104">
+        <v>0.602833333333333</v>
+      </c>
+      <c r="M99" s="105">
+        <v>0.593333333333333</v>
+      </c>
+      <c r="N99" s="82">
+        <v>0.603833333333333</v>
+      </c>
+      <c r="O99" s="100"/>
+    </row>
+    <row r="100" spans="4:16">
+      <c r="D100" s="73"/>
+      <c r="E100" s="73"/>
+      <c r="F100" s="73"/>
+      <c r="G100" s="73"/>
+      <c r="H100" s="73"/>
+      <c r="I100" s="73"/>
+      <c r="J100" s="73"/>
+      <c r="K100" s="20"/>
+      <c r="L100" s="20"/>
+      <c r="M100" s="20"/>
+      <c r="N100" s="20"/>
+      <c r="O100" s="20"/>
+      <c r="P100" s="19"/>
+    </row>
+    <row r="101" spans="11:16">
+      <c r="K101" s="106"/>
+      <c r="L101" s="20"/>
+      <c r="M101" s="20"/>
+      <c r="N101" s="106"/>
+      <c r="O101" s="20"/>
+      <c r="P101" s="19"/>
+    </row>
+    <row r="102" spans="16:16">
+      <c r="P102" s="20"/>
+    </row>
+    <row r="107" spans="4:14">
+      <c r="D107" s="31"/>
+      <c r="E107" s="31"/>
+      <c r="F107" s="31"/>
+      <c r="G107" s="31"/>
+      <c r="H107" s="31"/>
+      <c r="J107" s="31"/>
+      <c r="K107" s="31"/>
+      <c r="L107" s="31"/>
+      <c r="M107" s="31"/>
+      <c r="N107" s="31"/>
+    </row>
+    <row r="108" spans="4:14">
+      <c r="D108" s="31"/>
+      <c r="E108" s="31"/>
+      <c r="F108" s="31"/>
+      <c r="G108" s="31"/>
+      <c r="H108" s="31"/>
+      <c r="J108" s="31"/>
+      <c r="K108" s="31"/>
+      <c r="L108" s="31"/>
+      <c r="M108" s="31"/>
+      <c r="N108" s="31"/>
+    </row>
+    <row r="109" spans="12:14">
+      <c r="L109" s="106"/>
+      <c r="M109" s="20"/>
+      <c r="N109" s="20"/>
+    </row>
+    <row r="110" spans="6:14">
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+    </row>
+    <row r="111" spans="6:14">
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+    </row>
+    <row r="112" spans="6:14">
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="53">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:T3"/>
     <mergeCell ref="A4:B4"/>
@@ -3685,10 +4901,30 @@
     <mergeCell ref="S38:U38"/>
     <mergeCell ref="C52:E52"/>
     <mergeCell ref="F52:J52"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="J77:L77"/>
+    <mergeCell ref="M77:O77"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="M84:O84"/>
+    <mergeCell ref="F89:H89"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I94:I99"/>
+    <mergeCell ref="O94:O99"/>
     <mergeCell ref="A1:T2"/>
     <mergeCell ref="A33:Q34"/>
     <mergeCell ref="A44:C45"/>
     <mergeCell ref="A50:J51"/>
+    <mergeCell ref="D69:H70"/>
+    <mergeCell ref="D75:O76"/>
+    <mergeCell ref="D82:O83"/>
+    <mergeCell ref="J69:L70"/>
+    <mergeCell ref="D107:H108"/>
+    <mergeCell ref="J107:N108"/>
+    <mergeCell ref="D94:H95"/>
+    <mergeCell ref="J94:N95"/>
+    <mergeCell ref="L89:O93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
